--- a/assets/docs/lop1/Toan - Lop 1.xlsx
+++ b/assets/docs/lop1/Toan - Lop 1.xlsx
@@ -860,7 +860,8 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.
+STEM: Dụng cụ so sánh số (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -890,7 +891,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và đặt đúng dấu lớn hơn, bé hơn, bằng nhau giữa hai số.
+STEM: Dụng cụ so sánh số (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1102,8 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành cùng thẻ học Toán (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1133,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành cùng thẻ học Toán (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1234,8 @@
       <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - 1.C1.2: Hiểu camera là “mắt” giúp thiết bị/robot thu nhận hình ảnh; AI có thể xử lí hình ảnh để nhận diện các mảnh ghép khi thực hiện nhiệm vụ xếp hình.
-Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành trang trí lớp học bằng các hình hình học (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1266,8 @@
       <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - 1.C1.2: Hiểu camera là “mắt” giúp thiết bị/robot thu nhận hình ảnh; AI có thể xử lí hình ảnh để nhận diện các mảnh ghép khi thực hiện nhiệm vụ xếp hình.
-Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành trang trí lớp học bằng các hình hình học (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1744,8 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Dụng cụ tính cộng, tính trừ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1779,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Dụng cụ tính cộng, tính trừ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1810,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành tính nhẩm (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1841,8 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Thực hành tính nhẩm (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3156,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Mô hình tính hàng dọc (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3187,8 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Mô hình tính hàng dọc (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -3272,6 +3284,7 @@
         <is>
           <t>Tích hợp AI 1.A2.1: Kể tên được một số thiết bị có sử dụng AI như loa thông minh, trợ lý ảo; biết dưới sự hướng dẫn của giáo viên có thể hỏi trợ lý ảo về thời gian để hỗ trợ xem giờ và quản lí lịch trình cá nhân.
 Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Đồng hồ tiện ích (Toán – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN quản lí thời gian: xem giờ, sắp xếp công việc trong ngày.</t>
         </is>
       </c>
@@ -3302,7 +3315,8 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.</t>
+          <t>Năng lực số 1.1 CB1b: HS làm theo từng bước trong video hướng dẫn và hoàn thành sản phẩm của nhóm.
+STEM: Đồng hồ tiện ích (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
